--- a/matriz 2.xlsx
+++ b/matriz 2.xlsx
@@ -1,26 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ALBERTO\Desktop\JIME\TESTEANDO\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A647F86C-B9C7-4991-9B0F-ADE17A58204F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11596" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19200" windowHeight="8100"/>
   </bookViews>
   <sheets>
     <sheet name="Matriz de Adyacencia Simétrica " sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="61">
   <si>
     <t>Aitana</t>
   </si>
@@ -94,160 +101,498 @@
     <t>Sierra Helada</t>
   </si>
   <si>
+    <t>18.2</t>
+  </si>
+  <si>
+    <t>6.5</t>
+  </si>
+  <si>
+    <t>8.2</t>
+  </si>
+  <si>
+    <t>12.3</t>
+  </si>
+  <si>
+    <t>11.5</t>
+  </si>
+  <si>
+    <t>22.8</t>
+  </si>
+  <si>
     <t>50.1</t>
   </si>
   <si>
     <t>45.7</t>
   </si>
   <si>
+    <t>25.4</t>
+  </si>
+  <si>
     <t>38.6</t>
   </si>
   <si>
+    <t>12.5</t>
+  </si>
+  <si>
     <t>48.2</t>
   </si>
   <si>
+    <t>15.2</t>
+  </si>
+  <si>
+    <t>6.4</t>
+  </si>
+  <si>
+    <t>18.4</t>
+  </si>
+  <si>
+    <t>15.4</t>
+  </si>
+  <si>
+    <t>21.3</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>14.2</t>
+  </si>
+  <si>
+    <t>8.4</t>
+  </si>
+  <si>
+    <t>19.3</t>
+  </si>
+  <si>
+    <t>28.5</t>
+  </si>
+  <si>
+    <t>12.8</t>
+  </si>
+  <si>
+    <t>22.4</t>
+  </si>
+  <si>
+    <t>22.1</t>
+  </si>
+  <si>
+    <t>11.2</t>
+  </si>
+  <si>
+    <t>14.5</t>
+  </si>
+  <si>
+    <t>16.7</t>
+  </si>
+  <si>
+    <t>9.8</t>
+  </si>
+  <si>
+    <t>7.4</t>
+  </si>
+  <si>
+    <t>11.8</t>
+  </si>
+  <si>
+    <t>25.3</t>
+  </si>
+  <si>
     <t>45.2</t>
   </si>
   <si>
-    <t>18.2</t>
-  </si>
-  <si>
-    <t>8.2</t>
-  </si>
-  <si>
-    <t>12.3</t>
-  </si>
-  <si>
-    <t>11.5</t>
-  </si>
-  <si>
-    <t>18.4</t>
-  </si>
-  <si>
-    <t>6.4</t>
-  </si>
-  <si>
-    <t>12.5</t>
-  </si>
-  <si>
-    <t>15.2</t>
-  </si>
-  <si>
-    <t>22.8</t>
-  </si>
-  <si>
-    <t>25.4</t>
-  </si>
-  <si>
-    <t>6.5</t>
-  </si>
-  <si>
-    <t>25.1</t>
-  </si>
-  <si>
-    <t>15.4</t>
-  </si>
-  <si>
-    <t>21.3</t>
-  </si>
-  <si>
-    <t>4.2</t>
-  </si>
-  <si>
-    <t>14.2</t>
-  </si>
-  <si>
-    <t>8.4</t>
-  </si>
-  <si>
-    <t>19.3</t>
-  </si>
-  <si>
-    <t>28.5</t>
-  </si>
-  <si>
-    <t>12.8</t>
-  </si>
-  <si>
-    <t>22.4</t>
-  </si>
-  <si>
-    <t>22.1</t>
-  </si>
-  <si>
-    <t>11.2</t>
-  </si>
-  <si>
-    <t>14.5</t>
-  </si>
-  <si>
-    <t>16.7</t>
-  </si>
-  <si>
-    <t>9.8</t>
-  </si>
-  <si>
-    <t>10.5</t>
-  </si>
-  <si>
-    <t>7.4</t>
-  </si>
-  <si>
-    <t>25.3</t>
-  </si>
-  <si>
-    <t>11.8</t>
+    <t>5.6</t>
+  </si>
+  <si>
+    <t>5.8</t>
   </si>
   <si>
     <t>18.5</t>
   </si>
   <si>
     <t>12.1</t>
-  </si>
-  <si>
-    <t>5.8</t>
-  </si>
-  <si>
-    <t>5.6</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="d\.m"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="6">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-* #,##0.00\ &quot;€&quot;_-;\-* #,##0.00\ &quot;€&quot;_-;_-* \-??\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #,##0\ &quot;€&quot;_-;\-* #,##0\ &quot;€&quot;_-;_-* &quot;-&quot;\ &quot;€&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="d\,m"/>
+    <numFmt numFmtId="179" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="23">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
-      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -255,28 +600,316 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Coma" xfId="1" builtinId="3"/>
+    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
+    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
+    <cellStyle name="Coma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Moneda [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Hipervínculo" xfId="6" builtinId="8"/>
+    <cellStyle name="Hipervínculo visitado" xfId="7" builtinId="9"/>
+    <cellStyle name="Nota" xfId="8" builtinId="10"/>
+    <cellStyle name="Texto de advertencia" xfId="9" builtinId="11"/>
+    <cellStyle name="Título" xfId="10" builtinId="15"/>
+    <cellStyle name="Texto explicativo" xfId="11" builtinId="53"/>
+    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
+    <cellStyle name="Salida" xfId="17" builtinId="21"/>
+    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
+    <cellStyle name="Celda de comprobación" xfId="19" builtinId="23"/>
+    <cellStyle name="Celda vinculada" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Correcto" xfId="22" builtinId="26"/>
+    <cellStyle name="Incorrecto" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
+    <cellStyle name="Énfasis1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Énfasis1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Énfasis1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Énfasis1" xfId="28" builtinId="32"/>
+    <cellStyle name="Énfasis2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Énfasis2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Énfasis2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Énfasis2" xfId="32" builtinId="36"/>
+    <cellStyle name="Énfasis3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Énfasis3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Énfasis3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Énfasis3" xfId="36" builtinId="40"/>
+    <cellStyle name="Énfasis4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Énfasis4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Énfasis4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Énfasis4" xfId="40" builtinId="44"/>
+    <cellStyle name="Énfasis5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Énfasis5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Énfasis5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Énfasis5" xfId="44" builtinId="48"/>
+    <cellStyle name="Énfasis6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Énfasis6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Énfasis6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Énfasis6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -474,19 +1107,18 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:Y25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="12.59765625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="12.6017699115044" defaultRowHeight="15.75" customHeight="1"/>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="1" customHeight="1" spans="2:25">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -560,7 +1192,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="2" customHeight="1" spans="1:25">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,8 +1205,8 @@
       <c r="D2" s="1">
         <v>10000</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>29</v>
+      <c r="E2" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="F2" s="1">
         <v>10000</v>
@@ -603,8 +1235,8 @@
       <c r="N2" s="1">
         <v>10000</v>
       </c>
-      <c r="O2" s="4" t="s">
-        <v>39</v>
+      <c r="O2" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="P2" s="1">
         <v>10000</v>
@@ -615,14 +1247,14 @@
       <c r="R2" s="1">
         <v>10000</v>
       </c>
-      <c r="S2" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="T2" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="U2" s="4" t="s">
-        <v>32</v>
+      <c r="S2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="U2" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="V2" s="1">
         <v>10000</v>
@@ -637,7 +1269,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="3" customHeight="1" spans="1:25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -650,11 +1282,11 @@
       <c r="D3" s="1">
         <v>10000</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>37</v>
+      <c r="E3" s="2" t="s">
+        <v>29</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G3" s="1">
         <v>10000</v>
@@ -666,7 +1298,7 @@
         <v>10000</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K3" s="1">
         <v>10000</v>
@@ -677,8 +1309,8 @@
       <c r="M3" s="1">
         <v>10000</v>
       </c>
-      <c r="N3" s="2" t="s">
-        <v>38</v>
+      <c r="N3" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="O3" s="1">
         <v>10000</v>
@@ -689,8 +1321,8 @@
       <c r="Q3" s="1">
         <v>10000</v>
       </c>
-      <c r="R3" s="2" t="s">
-        <v>40</v>
+      <c r="R3" s="6">
+        <v>10000</v>
       </c>
       <c r="S3" s="1">
         <v>10000</v>
@@ -699,22 +1331,22 @@
         <v>10000</v>
       </c>
       <c r="U3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="V3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="W3" s="1">
+        <v>10000</v>
+      </c>
+      <c r="X3" s="1">
+        <v>10000</v>
+      </c>
+      <c r="Y3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="W3" s="1">
-        <v>10000</v>
-      </c>
-      <c r="X3" s="1">
-        <v>10000</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="4" customHeight="1" spans="1:25">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
@@ -772,7 +1404,7 @@
       <c r="S4" s="1">
         <v>10000</v>
       </c>
-      <c r="T4" s="4" t="s">
+      <c r="T4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="U4" s="1">
@@ -781,25 +1413,25 @@
       <c r="V4" s="1">
         <v>10000</v>
       </c>
-      <c r="W4" s="4" t="s">
-        <v>34</v>
+      <c r="W4" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="X4" s="1">
         <v>10000</v>
       </c>
-      <c r="Y4" s="4" t="s">
-        <v>33</v>
+      <c r="Y4" s="2" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="5" customHeight="1" spans="1:25">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>37</v>
       </c>
       <c r="D5" s="1">
         <v>10000</v>
@@ -843,8 +1475,8 @@
       <c r="Q5" s="1">
         <v>10000</v>
       </c>
-      <c r="R5" s="2" t="s">
-        <v>41</v>
+      <c r="R5" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="S5" s="1">
         <v>10000</v>
@@ -852,8 +1484,8 @@
       <c r="T5" s="1">
         <v>10000</v>
       </c>
-      <c r="U5" s="2" t="s">
-        <v>42</v>
+      <c r="U5" s="5" t="s">
+        <v>40</v>
       </c>
       <c r="V5" s="1">
         <v>10000</v>
@@ -868,7 +1500,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="6" customHeight="1" spans="1:25">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -876,7 +1508,7 @@
         <v>10000</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1">
         <v>10000</v>
@@ -896,8 +1528,8 @@
       <c r="I6" s="1">
         <v>10000</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>29</v>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="K6" s="1">
         <v>10000</v>
@@ -905,8 +1537,8 @@
       <c r="L6" s="1">
         <v>10000</v>
       </c>
-      <c r="M6" s="4" t="s">
-        <v>43</v>
+      <c r="M6" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="N6" s="1">
         <v>10000</v>
@@ -945,7 +1577,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="7" customHeight="1" spans="1:25">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -976,17 +1608,17 @@
       <c r="J7" s="1">
         <v>10000</v>
       </c>
-      <c r="K7" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>45</v>
+      <c r="K7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="M7" s="1">
         <v>10000</v>
       </c>
-      <c r="N7" s="2" t="s">
-        <v>31</v>
+      <c r="N7" s="5" t="s">
+        <v>27</v>
       </c>
       <c r="O7" s="1">
         <v>10000</v>
@@ -1022,7 +1654,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="8" customHeight="1" spans="1:25">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -1053,33 +1685,33 @@
       <c r="J8" s="1">
         <v>10000</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="M8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="N8" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="O8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="P8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="L8" s="1">
-        <v>10000</v>
-      </c>
-      <c r="M8" s="1">
-        <v>10000</v>
-      </c>
-      <c r="N8" s="2" t="s">
+      <c r="Q8" s="1">
+        <v>10000</v>
+      </c>
+      <c r="R8" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="O8" s="1">
-        <v>10000</v>
-      </c>
-      <c r="P8" s="2" t="s">
+      <c r="S8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="Q8" s="1">
-        <v>10000</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="T8" s="1">
         <v>10000</v>
       </c>
@@ -1099,7 +1731,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="9" customHeight="1" spans="1:25">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -1166,17 +1798,17 @@
       <c r="V9" s="1">
         <v>10000</v>
       </c>
-      <c r="W9" s="2" t="s">
+      <c r="W9" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="X9" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="X9" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="Y9" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="10" customHeight="1" spans="1:25">
       <c r="A10" s="1" t="s">
         <v>8</v>
       </c>
@@ -1184,7 +1816,7 @@
         <v>10000</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1">
         <v>10000</v>
@@ -1192,8 +1824,8 @@
       <c r="E10" s="1">
         <v>10000</v>
       </c>
-      <c r="F10" s="4" t="s">
-        <v>29</v>
+      <c r="F10" s="2" t="s">
+        <v>24</v>
       </c>
       <c r="G10" s="1">
         <v>10000</v>
@@ -1210,8 +1842,8 @@
       <c r="K10" s="1">
         <v>10000</v>
       </c>
-      <c r="L10" s="4" t="s">
-        <v>52</v>
+      <c r="L10" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="M10" s="1">
         <v>10000</v>
@@ -1253,7 +1885,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="11" customHeight="1" spans="1:25">
       <c r="A11" s="1" t="s">
         <v>9</v>
       </c>
@@ -1272,11 +1904,11 @@
       <c r="F11" s="1">
         <v>10000</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="I11" s="1">
         <v>10000</v>
@@ -1293,8 +1925,8 @@
       <c r="M11" s="1">
         <v>10000</v>
       </c>
-      <c r="N11" s="2" t="s">
-        <v>53</v>
+      <c r="N11" s="5" t="s">
+        <v>51</v>
       </c>
       <c r="O11" s="1">
         <v>10000</v>
@@ -1330,7 +1962,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="12" customHeight="1" spans="1:25">
       <c r="A12" s="1" t="s">
         <v>10</v>
       </c>
@@ -1349,8 +1981,8 @@
       <c r="F12" s="1">
         <v>10000</v>
       </c>
-      <c r="G12" s="4" t="s">
-        <v>45</v>
+      <c r="G12" s="2" t="s">
+        <v>43</v>
       </c>
       <c r="H12" s="1">
         <v>10000</v>
@@ -1358,8 +1990,8 @@
       <c r="I12" s="1">
         <v>10000</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>52</v>
+      <c r="J12" s="2" t="s">
+        <v>50</v>
       </c>
       <c r="K12" s="1">
         <v>10000</v>
@@ -1394,8 +2026,8 @@
       <c r="U12" s="1">
         <v>10000</v>
       </c>
-      <c r="V12" s="2" t="s">
-        <v>54</v>
+      <c r="V12" s="5" t="s">
+        <v>52</v>
       </c>
       <c r="W12" s="1">
         <v>10000</v>
@@ -1407,7 +2039,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="13" customHeight="1" spans="1:25">
       <c r="A13" s="1" t="s">
         <v>11</v>
       </c>
@@ -1423,8 +2055,8 @@
       <c r="E13" s="1">
         <v>10000</v>
       </c>
-      <c r="F13" s="4" t="s">
-        <v>43</v>
+      <c r="F13" s="2" t="s">
+        <v>41</v>
       </c>
       <c r="G13" s="1">
         <v>10000</v>
@@ -1484,15 +2116,15 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="14" customHeight="1" spans="1:25">
       <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B14" s="1">
         <v>10000</v>
       </c>
-      <c r="C14" s="4" t="s">
-        <v>38</v>
+      <c r="C14" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="D14" s="1">
         <v>10000</v>
@@ -1503,11 +2135,11 @@
       <c r="F14" s="1">
         <v>10000</v>
       </c>
-      <c r="G14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>47</v>
+      <c r="G14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>45</v>
       </c>
       <c r="I14" s="1">
         <v>10000</v>
@@ -1515,8 +2147,8 @@
       <c r="J14" s="1">
         <v>10000</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>53</v>
+      <c r="K14" s="2" t="s">
+        <v>51</v>
       </c>
       <c r="L14" s="1">
         <v>10000</v>
@@ -1536,8 +2168,8 @@
       <c r="Q14" s="1">
         <v>10000</v>
       </c>
-      <c r="R14" s="2" t="s">
-        <v>55</v>
+      <c r="R14" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="S14" s="1">
         <v>10000</v>
@@ -1561,12 +2193,12 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="15" customHeight="1" spans="1:25">
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>39</v>
+      <c r="B15" s="2" t="s">
+        <v>25</v>
       </c>
       <c r="C15" s="1">
         <v>10000</v>
@@ -1616,11 +2248,11 @@
       <c r="R15" s="1">
         <v>10000</v>
       </c>
-      <c r="S15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>58</v>
+      <c r="S15" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="T15" s="5" t="s">
+        <v>54</v>
       </c>
       <c r="U15" s="1">
         <v>10000</v>
@@ -1631,14 +2263,14 @@
       <c r="W15" s="1">
         <v>10000</v>
       </c>
-      <c r="X15" s="2" t="s">
-        <v>57</v>
+      <c r="X15" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="Y15" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="16" customHeight="1" spans="1:25">
       <c r="A16" s="1" t="s">
         <v>14</v>
       </c>
@@ -1660,8 +2292,8 @@
       <c r="G16" s="1">
         <v>10000</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>48</v>
+      <c r="H16" s="2" t="s">
+        <v>46</v>
       </c>
       <c r="I16" s="1">
         <v>10000</v>
@@ -1693,8 +2325,8 @@
       <c r="R16" s="1">
         <v>10000</v>
       </c>
-      <c r="S16" s="2" t="s">
-        <v>41</v>
+      <c r="S16" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="T16" s="1">
         <v>10000</v>
@@ -1709,13 +2341,13 @@
         <v>10000</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="Y16" s="1">
         <v>10000</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="17" customHeight="1" spans="1:25">
       <c r="A17" s="1" t="s">
         <v>15</v>
       </c>
@@ -1782,8 +2414,8 @@
       <c r="V17" s="1">
         <v>10000</v>
       </c>
-      <c r="W17" s="2" t="s">
-        <v>62</v>
+      <c r="W17" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="X17" s="1">
         <v>10000</v>
@@ -1792,21 +2424,21 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="18" customHeight="1" spans="1:25">
       <c r="A18" s="1" t="s">
         <v>16</v>
       </c>
       <c r="B18" s="1">
         <v>10000</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>40</v>
+      <c r="C18" s="4">
+        <v>10000</v>
       </c>
       <c r="D18" s="1">
         <v>10000</v>
       </c>
-      <c r="E18" s="4" t="s">
-        <v>41</v>
+      <c r="E18" s="2" t="s">
+        <v>39</v>
       </c>
       <c r="F18" s="1">
         <v>10000</v>
@@ -1814,8 +2446,8 @@
       <c r="G18" s="1">
         <v>10000</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>49</v>
+      <c r="H18" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="I18" s="1">
         <v>10000</v>
@@ -1832,8 +2464,8 @@
       <c r="M18" s="1">
         <v>10000</v>
       </c>
-      <c r="N18" s="2" t="s">
-        <v>55</v>
+      <c r="N18" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="O18" s="1">
         <v>10000</v>
@@ -1869,12 +2501,12 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="19" customHeight="1" spans="1:25">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>30</v>
+      <c r="B19" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="C19" s="1">
         <v>10000</v>
@@ -1891,8 +2523,8 @@
       <c r="G19" s="1">
         <v>10000</v>
       </c>
-      <c r="H19" s="4" t="s">
-        <v>50</v>
+      <c r="H19" s="2" t="s">
+        <v>48</v>
       </c>
       <c r="I19" s="1">
         <v>10000</v>
@@ -1912,11 +2544,11 @@
       <c r="N19" s="1">
         <v>10000</v>
       </c>
-      <c r="O19" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="P19" s="2" t="s">
-        <v>41</v>
+      <c r="O19" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="P19" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="Q19" s="1">
         <v>10000</v>
@@ -1946,17 +2578,17 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="20" customHeight="1" spans="1:25">
       <c r="A20" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>31</v>
+      <c r="B20" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="C20" s="1">
         <v>10000</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="2" t="s">
         <v>36</v>
       </c>
       <c r="E20" s="1">
@@ -1989,8 +2621,8 @@
       <c r="N20" s="1">
         <v>10000</v>
       </c>
-      <c r="O20" s="4" t="s">
-        <v>58</v>
+      <c r="O20" s="2" t="s">
+        <v>54</v>
       </c>
       <c r="P20" s="1">
         <v>10000</v>
@@ -2007,37 +2639,37 @@
       <c r="T20" s="1">
         <v>0</v>
       </c>
-      <c r="U20" s="2" t="s">
-        <v>61</v>
+      <c r="U20" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="V20" s="1">
         <v>10000</v>
       </c>
-      <c r="W20" s="2" t="s">
+      <c r="W20" s="5" t="s">
         <v>59</v>
       </c>
       <c r="X20" s="1">
         <v>10000</v>
       </c>
-      <c r="Y20" s="2" t="s">
+      <c r="Y20" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="21" customHeight="1" spans="1:25">
       <c r="A21" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>32</v>
+      <c r="B21" s="2" t="s">
+        <v>28</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D21" s="1">
         <v>10000</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>42</v>
+      <c r="E21" s="2" t="s">
+        <v>40</v>
       </c>
       <c r="F21" s="1">
         <v>10000</v>
@@ -2081,8 +2713,8 @@
       <c r="S21" s="1">
         <v>10000</v>
       </c>
-      <c r="T21" s="2" t="s">
-        <v>61</v>
+      <c r="T21" s="5" t="s">
+        <v>58</v>
       </c>
       <c r="U21" s="1">
         <v>0</v>
@@ -2096,19 +2728,19 @@
       <c r="X21" s="1">
         <v>10000</v>
       </c>
-      <c r="Y21" s="2" t="s">
-        <v>41</v>
+      <c r="Y21" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="22" customHeight="1" spans="1:25">
       <c r="A22" s="1" t="s">
         <v>20</v>
       </c>
       <c r="B22" s="1">
         <v>10000</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>35</v>
+      <c r="C22" s="2" t="s">
+        <v>34</v>
       </c>
       <c r="D22" s="1">
         <v>10000</v>
@@ -2134,8 +2766,8 @@
       <c r="K22" s="1">
         <v>10000</v>
       </c>
-      <c r="L22" s="4" t="s">
-        <v>54</v>
+      <c r="L22" s="2" t="s">
+        <v>52</v>
       </c>
       <c r="M22" s="1">
         <v>10000</v>
@@ -2177,7 +2809,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="23" customHeight="1" spans="1:25">
       <c r="A23" s="1" t="s">
         <v>21</v>
       </c>
@@ -2187,8 +2819,8 @@
       <c r="C23" s="1">
         <v>10000</v>
       </c>
-      <c r="D23" s="4" t="s">
-        <v>34</v>
+      <c r="D23" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="E23" s="1">
         <v>10000</v>
@@ -2202,8 +2834,8 @@
       <c r="H23" s="1">
         <v>10000</v>
       </c>
-      <c r="I23" s="4" t="s">
-        <v>49</v>
+      <c r="I23" s="2" t="s">
+        <v>47</v>
       </c>
       <c r="J23" s="1">
         <v>10000</v>
@@ -2226,8 +2858,8 @@
       <c r="P23" s="1">
         <v>10000</v>
       </c>
-      <c r="Q23" s="2" t="s">
-        <v>62</v>
+      <c r="Q23" s="5" t="s">
+        <v>57</v>
       </c>
       <c r="R23" s="1">
         <v>10000</v>
@@ -2235,7 +2867,7 @@
       <c r="S23" s="1">
         <v>10000</v>
       </c>
-      <c r="T23" s="2" t="s">
+      <c r="T23" s="5" t="s">
         <v>59</v>
       </c>
       <c r="U23" s="1">
@@ -2254,7 +2886,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="24" customHeight="1" spans="1:25">
       <c r="A24" s="1" t="s">
         <v>22</v>
       </c>
@@ -2279,8 +2911,8 @@
       <c r="H24" s="1">
         <v>10000</v>
       </c>
-      <c r="I24" s="4" t="s">
-        <v>51</v>
+      <c r="I24" s="2" t="s">
+        <v>49</v>
       </c>
       <c r="J24" s="1">
         <v>10000</v>
@@ -2297,11 +2929,11 @@
       <c r="N24" s="1">
         <v>10000</v>
       </c>
-      <c r="O24" s="2" t="s">
-        <v>57</v>
+      <c r="O24" s="5" t="s">
+        <v>55</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="Q24" s="1">
         <v>10000</v>
@@ -2331,7 +2963,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+    <row r="25" customHeight="1" spans="1:25">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -2339,10 +2971,10 @@
         <v>10000</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>38</v>
       </c>
       <c r="E25" s="1">
         <v>10000</v>
@@ -2389,11 +3021,11 @@
       <c r="S25" s="1">
         <v>10000</v>
       </c>
-      <c r="T25" s="2" t="s">
+      <c r="T25" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="U25" s="2" t="s">
-        <v>41</v>
+      <c r="U25" s="5" t="s">
+        <v>39</v>
       </c>
       <c r="V25" s="1">
         <v>10000</v>
@@ -2410,6 +3042,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>